--- a/InputData/ccs/BCS/BAU CCS Subsidy.xlsx
+++ b/InputData/ccs/BCS/BAU CCS Subsidy.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\ccs\BCS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndiaEPS/Shared Documents/Completed EPS Variables/ccs/BCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F268FE25-6FA1-4964-97BE-7705BD55074C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{BE6010A5-9296-4BCB-89A5-8BC51C00131D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C69687C6-3B7D-432E-933B-6C1C1AD41FFB}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -47,14 +47,20 @@
     <definedName name="solver_val" localSheetId="0" hidden="1">0.15</definedName>
     <definedName name="solver_ver" localSheetId="0" hidden="1">3</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -62,63 +68,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>BCS BAU CCS Subsidy</t>
+  </si>
   <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>None needed</t>
+  </si>
+  <si>
     <t>Notes:</t>
   </si>
   <si>
+    <t>This variable captures any BAU subsidies for CCS, specified in dollars per ton captured.</t>
+  </si>
+  <si>
+    <t>For electricity, adjust the credit value based on its duration relative to the financing repayment period</t>
+  </si>
+  <si>
+    <t>2022 to 2012 USD</t>
+  </si>
+  <si>
+    <t>45Q Tax Credit Amount</t>
+  </si>
+  <si>
+    <t>Credit Amount</t>
+  </si>
+  <si>
+    <t>Repayment Period for Financing</t>
+  </si>
+  <si>
+    <t>45Q Credit Duration</t>
+  </si>
+  <si>
+    <t>Credit Value</t>
+  </si>
+  <si>
+    <t>$ / metric ton</t>
+  </si>
+  <si>
     <t>electricity sector</t>
   </si>
   <si>
     <t>industry sector</t>
   </si>
   <si>
-    <t>None needed</t>
-  </si>
-  <si>
-    <t>2022 to 2012 USD</t>
-  </si>
-  <si>
-    <t>This variable captures any BAU subsidies for CCS, specified in dollars per ton captured.</t>
-  </si>
-  <si>
-    <t>BCS BAU CCS Subsidy</t>
-  </si>
-  <si>
-    <t>$ / metric ton</t>
-  </si>
-  <si>
-    <t>45Q Tax Credit Amount</t>
-  </si>
-  <si>
-    <t>Credit Amount</t>
-  </si>
-  <si>
-    <t>Repayment Period for Financing</t>
-  </si>
-  <si>
-    <t>45Q Credit Duration</t>
-  </si>
-  <si>
-    <t>Credit Value</t>
-  </si>
-  <si>
-    <t>For electricity, adjust the credit value based on its duration relative to the financing repayment period</t>
+    <t>For India, values are zero as no subsidy for CCS have been announced</t>
   </si>
   <si>
     <t>Years</t>
   </si>
   <si>
     <t>Duration</t>
-  </si>
-  <si>
-    <t>45Q Duration</t>
-  </si>
-  <si>
-    <t>12 years</t>
   </si>
 </sst>
 </file>
@@ -491,64 +494,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.33203125" customWidth="1"/>
-    <col min="2" max="2" width="55.88671875" customWidth="1"/>
-    <col min="4" max="4" width="30.5546875" customWidth="1"/>
+    <col min="1" max="1" width="30.26953125" customWidth="1"/>
+    <col min="2" max="2" width="55.81640625" customWidth="1"/>
+    <col min="4" max="4" width="30.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>0.78500000000000003</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11" s="6">
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -560,39 +560,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AB35C55-7F27-44A6-A8A7-496D78F28576}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B1" s="7">
         <f>About!B11</f>
         <v>85</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="7">
         <f>B1*B3/B2</f>
@@ -609,16 +609,16 @@
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:AE3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AY3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.44140625" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="1" max="1" width="19.453125" customWidth="1"/>
+    <col min="2" max="2" width="24.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B1" s="2">
         <v>2021</v>
@@ -710,10 +710,70 @@
       <c r="AE1" s="2">
         <v>2050</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AF1" s="2">
+        <v>2051</v>
+      </c>
+      <c r="AG1" s="2">
+        <v>2052</v>
+      </c>
+      <c r="AH1" s="2">
+        <v>2053</v>
+      </c>
+      <c r="AI1" s="2">
+        <v>2054</v>
+      </c>
+      <c r="AJ1" s="2">
+        <v>2055</v>
+      </c>
+      <c r="AK1" s="2">
+        <v>2056</v>
+      </c>
+      <c r="AL1" s="2">
+        <v>2057</v>
+      </c>
+      <c r="AM1" s="2">
+        <v>2058</v>
+      </c>
+      <c r="AN1" s="2">
+        <v>2059</v>
+      </c>
+      <c r="AO1" s="2">
+        <v>2060</v>
+      </c>
+      <c r="AP1" s="2">
+        <v>2061</v>
+      </c>
+      <c r="AQ1" s="2">
+        <v>2062</v>
+      </c>
+      <c r="AR1" s="2">
+        <v>2063</v>
+      </c>
+      <c r="AS1" s="2">
+        <v>2064</v>
+      </c>
+      <c r="AT1" s="2">
+        <v>2065</v>
+      </c>
+      <c r="AU1" s="2">
+        <v>2066</v>
+      </c>
+      <c r="AV1" s="2">
+        <v>2067</v>
+      </c>
+      <c r="AW1" s="2">
+        <v>2068</v>
+      </c>
+      <c r="AX1" s="2">
+        <v>2069</v>
+      </c>
+      <c r="AY1" s="2">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B2" s="4">
         <v>0</v>
@@ -721,104 +781,154 @@
       <c r="C2" s="4">
         <v>0</v>
       </c>
-      <c r="D2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="E2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="F2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="G2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="H2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="I2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="J2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="K2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="L2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="M2">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+      <c r="R2" s="4">
+        <v>0</v>
+      </c>
+      <c r="S2" s="4">
+        <v>0</v>
+      </c>
+      <c r="T2" s="4">
+        <v>0</v>
+      </c>
+      <c r="U2" s="4">
+        <v>0</v>
+      </c>
+      <c r="V2" s="4">
+        <v>0</v>
+      </c>
+      <c r="W2" s="4">
+        <v>0</v>
+      </c>
+      <c r="X2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX2" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:51" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B3" s="4">
         <v>0</v>
@@ -826,83 +936,73 @@
       <c r="C3" s="4">
         <v>0</v>
       </c>
-      <c r="D3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="E3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="F3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="G3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="H3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="I3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="J3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="K3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="L3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="M3">
-        <f>About!$B$11*About!$A$9</f>
-        <v>66.725000000000009</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="V3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+      <c r="R3" s="4">
+        <v>0</v>
+      </c>
+      <c r="S3" s="4">
+        <v>0</v>
+      </c>
+      <c r="T3" s="4">
+        <v>0</v>
+      </c>
+      <c r="U3" s="4">
+        <v>0</v>
+      </c>
+      <c r="V3" s="4">
+        <v>0</v>
+      </c>
+      <c r="W3" s="4">
+        <v>0</v>
+      </c>
+      <c r="X3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="4">
         <v>0</v>
       </c>
       <c r="AA3">
@@ -917,7 +1017,67 @@
       <c r="AD3">
         <v>0</v>
       </c>
-      <c r="AE3">
+      <c r="AE3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AX3" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY3" s="4">
         <v>0</v>
       </c>
     </row>
@@ -927,16 +1087,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5698252-CD29-4D86-9D7F-2214C5598602}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3809C3E1-6516-465A-AEE7-962768A4FB8A}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B1">
         <v>2021</v>
@@ -1029,131 +1189,310 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <f>$B$2</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D2">
         <f>$B$2</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <f t="shared" ref="E2:AE2" si="0">$B$2</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="X2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AB2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AD2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2EDDEA3-8531-4158-903E-EDA5ECE6D978}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A87A5F25-FED6-4313-8E0A-BBDEDCD810F8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>